--- a/RETEN-REC.xlsx
+++ b/RETEN-REC.xlsx
@@ -5,21 +5,305 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Freddy Lopez\proyecto-tesis-app-version-3.1\bot_financiero_telegram\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Freddy Lopez\Documents\Telegram bot\bot_financiero_telegram\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="5688"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072"/>
   </bookViews>
   <sheets>
-    <sheet name="Retenciones" sheetId="1" r:id="rId1"/>
+    <sheet name="Consolidado" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="73">
+  <si>
+    <t>Fecha_emision</t>
+  </si>
+  <si>
+    <t>Numero_comprobante</t>
+  </si>
+  <si>
+    <t>RIF</t>
+  </si>
+  <si>
+    <t>Fechas_facturas</t>
+  </si>
+  <si>
+    <t>Numeros_facturas</t>
+  </si>
+  <si>
+    <t>Controles_facturas</t>
+  </si>
+  <si>
+    <t>Total_compra_con_iva</t>
+  </si>
+  <si>
+    <t>Base_imponible</t>
+  </si>
+  <si>
+    <t>IVA_retenido</t>
+  </si>
+  <si>
+    <t>Fecha_registro</t>
+  </si>
+  <si>
+    <t>Texto_OCR_resumen</t>
+  </si>
+  <si>
+    <t>30-05-2026</t>
+  </si>
+  <si>
+    <t>20260500000731</t>
+  </si>
+  <si>
+    <t>J-314810928</t>
+  </si>
+  <si>
+    <t>00007736</t>
+  </si>
+  <si>
+    <t>Z7C7018762</t>
+  </si>
+  <si>
+    <t>Bs. 86,012.23</t>
+  </si>
+  <si>
+    <t>Bs. 74,148.47</t>
+  </si>
+  <si>
+    <t>Bs. 8,897.82</t>
+  </si>
+  <si>
+    <t>2026-05-30T15:40:34</t>
+  </si>
+  <si>
+    <t>Registro manual de la retencion solicitada por el usuario en chat.</t>
+  </si>
+  <si>
+    <t>26/05/2026</t>
+  </si>
+  <si>
+    <t>20260500000484</t>
+  </si>
+  <si>
+    <t>J-41278020-4</t>
+  </si>
+  <si>
+    <t>00007716</t>
+  </si>
+  <si>
+    <t>Bs. 6,610.00</t>
+  </si>
+  <si>
+    <t>Bs. 5,698.28</t>
+  </si>
+  <si>
+    <t>Bs. 683.79</t>
+  </si>
+  <si>
+    <t>2026-05-30T16:11:08</t>
+  </si>
+  <si>
+    <t>Registro manual de la retencion solicitada por el usuario en chat (SUMINISTROS VAF).</t>
+  </si>
+  <si>
+    <t>20-05-2026</t>
+  </si>
+  <si>
+    <t>2026050000082</t>
+  </si>
+  <si>
+    <t>V-082516375</t>
+  </si>
+  <si>
+    <t>00007695</t>
+  </si>
+  <si>
+    <t>Bs. 53.984,93</t>
+  </si>
+  <si>
+    <t>Bs. 46.538,73</t>
+  </si>
+  <si>
+    <t>Bs. 5.584,65</t>
+  </si>
+  <si>
+    <t>2026-05-30T16:15:01</t>
+  </si>
+  <si>
+    <t>Comprobante de retencion (registro manual texto/voz). Retenciones Recibidas
+Datos del Comprobante:
+Fecha de Emisión: 20-05-2026
+Número de Comprobante: 2026050000082
+Datos del Cliente (Agente de Retención)
+Nombre o Razón Social: MARCOS ANTONIO GUERRA GUZMAN (GUERRA MULTISERVICIOS ABNER, F.P)
+RIF: V-082516375
+Datos de la Factura Afectada
+Número de Factura: 00007695
+Número de Control: Z7C7018762
+Desglose Financiero (Bolívares)
+Total Factura: Bs. 53.984,93
+Base Imponible: B</t>
+  </si>
+  <si>
+    <t>18-05-2026</t>
+  </si>
+  <si>
+    <t>20260500007143</t>
+  </si>
+  <si>
+    <t>J302462916</t>
+  </si>
+  <si>
+    <t>00007680</t>
+  </si>
+  <si>
+    <t>Bs. 12.576,00</t>
+  </si>
+  <si>
+    <t>Bs. 10.841,38</t>
+  </si>
+  <si>
+    <t>Bs. 1.300,97</t>
+  </si>
+  <si>
+    <t>2026-05-30T16:15:24</t>
+  </si>
+  <si>
+    <t>Comprobante de retencion (registro manual texto/voz). Retenciones Recibidas
+Datos del Comprobante:
+Fecha de Emisión: 18-05-2026
+Número de Comprobante: 20260500007143
+Datos del Cliente (Agente de Retención)
+Nombre o Razón Social: LUBVENCA ORIENTE C.A
+RIF: J302462916
+Datos de la Factura Afectada
+Número de Factura: 00007680
+Número de Control: Z7C7018762
+Desglose Financiero (Bolívares)
+Total Factura: Bs. 12.576,00
+Base Imponible: Bs. 10.841,38
+Porcentaje de Retención:
+Impue</t>
+  </si>
+  <si>
+    <t>16-05-2026</t>
+  </si>
+  <si>
+    <t>2026050000081</t>
+  </si>
+  <si>
+    <t>00007666</t>
+  </si>
+  <si>
+    <t>Bs. 16.481,98</t>
+  </si>
+  <si>
+    <t>Bs. 14.208,60</t>
+  </si>
+  <si>
+    <t>Bs. 1.705,03</t>
+  </si>
+  <si>
+    <t>2026-05-30T16:15:34</t>
+  </si>
+  <si>
+    <t>Comprobante de retencion (registro manual texto/voz). Retenciones Recibidas
+Datos del Comprobante:
+Fecha de Emisión: 16-05-2026
+Número de Comprobante: 2026050000081
+Datos del Cliente (Agente de Retención)
+Nombre o Razón Social: MARCOS ANTONIO GUERRA GUZMAN (GUERRA MULTISERVICIOS ABNER, F.P)
+RIF: V-082516375
+Datos de la Factura Afectada
+Número de Factura: 00007666
+Número de Control: Z7C7018762
+Desglose Financiero (Bolívares)
+Total Factura: Bs. 16.481,98
+Base Imponible: B</t>
+  </si>
+  <si>
+    <t>20/05/2026</t>
+  </si>
+  <si>
+    <t>20260500051199</t>
+  </si>
+  <si>
+    <t>J080231686</t>
+  </si>
+  <si>
+    <t>00007685</t>
+  </si>
+  <si>
+    <t>Bs. 6.122.920,74</t>
+  </si>
+  <si>
+    <t>Bs. 5.278.379,95</t>
+  </si>
+  <si>
+    <t>Bs. 633.405,59</t>
+  </si>
+  <si>
+    <t>2026-05-30T16:15:43</t>
+  </si>
+  <si>
+    <t>Comprobante de retencion (registro manual texto/voz). Retenciones Recibidas
+Datos del Comprobante:
+Fecha de Emisión: 20/05/2026
+Número de Comprobante: 20260500051199
+Datos del Cliente (Agente de Retención)
+Nombre o Razón Social: UNIVERSIDAD GRAN MARISCAL DE AYACUCHO
+RIF: J080231686
+Datos de la Factura Afectada
+Número de Factura: 00007685
+Número de Control: Z7C7018762
+Desglose Financiero (Bolívares)
+Total Factura: Bs. 6.122.920,74
+Base Imponible: Bs. 5.278.379,95
+Porcent</t>
+  </si>
+  <si>
+    <t>20260500000408</t>
+  </si>
+  <si>
+    <t>J505065068</t>
+  </si>
+  <si>
+    <t>00007638</t>
+  </si>
+  <si>
+    <t>Bs. 1.340,00</t>
+  </si>
+  <si>
+    <t>Bs. 1.155,17</t>
+  </si>
+  <si>
+    <t>Bs. 138,62</t>
+  </si>
+  <si>
+    <t>2026-05-30T22:42:22</t>
+  </si>
+  <si>
+    <t>Comprobante de retencion (registro manual texto/voz). Retenciones Recibidas
+Datos del Comprobante:
+Fecha de Emisión: 12/05/2026
+Número de Comprobante: 20260500000408
+Datos del Cliente (Agente de Retención)
+Nombre o Razón Social: AGROTIENDA LA ECONOMICA DE ORIENTE, C.A
+RIF: J505065068
+Datos de la Factura Afectada
+Número de Factura: 00007638
+Número de Control: Z7C7018762
+Desglose Financiero (Bolívares)
+Total Factura: Bs. 1.340,00
+Base Imponible: Bs. 1.155,17
+Porcentaje de</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -53,8 +337,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -357,9 +642,278 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4" t="s">
+        <v>37</v>
+      </c>
+      <c r="K4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H5" t="s">
+        <v>44</v>
+      </c>
+      <c r="I5" t="s">
+        <v>45</v>
+      </c>
+      <c r="J5" t="s">
+        <v>46</v>
+      </c>
+      <c r="K5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" t="s">
+        <v>51</v>
+      </c>
+      <c r="H6" t="s">
+        <v>52</v>
+      </c>
+      <c r="I6" t="s">
+        <v>53</v>
+      </c>
+      <c r="J6" t="s">
+        <v>54</v>
+      </c>
+      <c r="K6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" t="s">
+        <v>60</v>
+      </c>
+      <c r="H7" t="s">
+        <v>61</v>
+      </c>
+      <c r="I7" t="s">
+        <v>62</v>
+      </c>
+      <c r="J7" t="s">
+        <v>63</v>
+      </c>
+      <c r="K7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>46158</v>
+      </c>
+      <c r="B8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E8" t="s">
+        <v>67</v>
+      </c>
+      <c r="F8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" t="s">
+        <v>68</v>
+      </c>
+      <c r="H8" t="s">
+        <v>69</v>
+      </c>
+      <c r="I8" t="s">
+        <v>70</v>
+      </c>
+      <c r="J8" t="s">
+        <v>71</v>
+      </c>
+      <c r="K8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="I9">
+        <f>SUM(I2:I8)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>